--- a/data/trans_bre/P16A05-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A05-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 2,4</t>
+          <t>-1,21; 2,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,88</t>
+          <t>1,37; 5,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 7,63</t>
+          <t>3,13; 7,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,91</t>
+          <t>0,74; 4,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,72; 114,79</t>
+          <t>-34,09; 113,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,08; 237,73</t>
+          <t>27,51; 242,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,22; 464,61</t>
+          <t>81,11; 478,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,29; 152,16</t>
+          <t>10,94; 150,36</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,96</t>
+          <t>1,37; 4,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 7,25</t>
+          <t>3,28; 7,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 5,57</t>
+          <t>1,73; 5,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,76; 9,93</t>
+          <t>5,62; 9,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,57; 264,31</t>
+          <t>39,67; 271,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>75,8; 327,01</t>
+          <t>79,23; 327,89</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,43; 235,07</t>
+          <t>38,2; 248,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>148,8; 726,84</t>
+          <t>151,36; 694,14</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,62; 6,86</t>
+          <t>3,02; 7,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 5,26</t>
+          <t>0,16; 4,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 5,98</t>
+          <t>1,04; 5,62</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 3,53</t>
+          <t>-2,87; 3,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82,64; 524,73</t>
+          <t>94,54; 551,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 235,85</t>
+          <t>0,88; 227,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,3; 201,87</t>
+          <t>20,24; 199,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-42,27; 85,79</t>
+          <t>-42,13; 89,18</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 4,24</t>
+          <t>0,83; 4,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 5,36</t>
+          <t>1,14; 5,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,91</t>
+          <t>2,18; 6,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 5,43</t>
+          <t>0,57; 5,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,28; 202,59</t>
+          <t>22,63; 210,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,47; 181,82</t>
+          <t>20,43; 198,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,15; 200,22</t>
+          <t>38,69; 189,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,59; 129,93</t>
+          <t>10,91; 136,14</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,67</t>
+          <t>1,74; 3,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,52; 4,76</t>
+          <t>2,59; 4,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,02; 5,35</t>
+          <t>3,09; 5,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,17</t>
+          <t>2,32; 5,26</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>57,93; 164,74</t>
+          <t>58,49; 167,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,66; 167,26</t>
+          <t>67,08; 171,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>77,32; 173,45</t>
+          <t>76,87; 174,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>54,4; 155,71</t>
+          <t>52,4; 157,61</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A05-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P16A05-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>2,65</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>59,36%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,32</t>
+          <t>-1,44; 2,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 5,95</t>
+          <t>1,1; 6,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,13; 7,82</t>
+          <t>2,89; 7,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,9</t>
+          <t>0,4; 4,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-34,09; 113,6</t>
+          <t>-37,6; 96,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,51; 242,15</t>
+          <t>21,65; 231,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,11; 478,8</t>
+          <t>73,29; 453,33</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,94; 150,36</t>
+          <t>6,65; 140,42</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,67</t>
+          <t>6,99</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>289,01%</t>
+          <t>222,77%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,98</t>
+          <t>1,3; 5,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,38</t>
+          <t>3,19; 7,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,72</t>
+          <t>1,56; 5,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,62; 9,9</t>
+          <t>5,12; 8,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,67; 271,02</t>
+          <t>35,21; 276,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,23; 327,89</t>
+          <t>78,76; 332,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,2; 248,65</t>
+          <t>38,98; 232,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>151,36; 694,14</t>
+          <t>124,68; 386,68</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,87</t>
+          <t>2,48</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>50,67%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,04</t>
+          <t>2,84; 7,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 4,87</t>
+          <t>0,28; 5,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,62</t>
+          <t>1,07; 6,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 3,63</t>
+          <t>0,26; 4,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>94,54; 551,59</t>
+          <t>94,26; 600,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 227,71</t>
+          <t>1,67; 235,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,24; 199,69</t>
+          <t>18,57; 206,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-42,13; 89,18</t>
+          <t>3,99; 130,55</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>3,59</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>75,07%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,35</t>
+          <t>0,57; 4,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,36</t>
+          <t>1,41; 5,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,55</t>
+          <t>2,14; 6,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 5,39</t>
+          <t>1,81; 5,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,63; 210,7</t>
+          <t>13,46; 202,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,43; 198,09</t>
+          <t>26,9; 212,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,69; 189,89</t>
+          <t>37,59; 193,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,91; 136,14</t>
+          <t>29,92; 136,76</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,86</t>
+          <t>4,16</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>97,57%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,64</t>
+          <t>1,76; 3,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,86</t>
+          <t>2,68; 4,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,09; 5,34</t>
+          <t>3,05; 5,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,26</t>
+          <t>3,11; 5,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,49; 167,3</t>
+          <t>58,07; 164,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>67,08; 171,7</t>
+          <t>67,04; 166,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,87; 174,9</t>
+          <t>77,07; 173,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>52,4; 157,61</t>
+          <t>65,43; 137,06</t>
         </is>
       </c>
     </row>
